--- a/exports/quality/notebook_02_quality_report.xlsx
+++ b/exports/quality/notebook_02_quality_report.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'Current_Portfolio': 0.0001354, 'Max_Return': 0.0, 'MeanVariance_TurnoverPenalty': 0.00617435, 'Mean_CVaR_95': 0.00202696, 'Mean_Variance_lambda_10': 1e-08, 'Mean_Variance_lambda_2': 0.0, 'Mean_Variance_lambda_20': 0.00617436, 'Mean_Variance_lambda_5': 0.0, 'Minimum_Variance': 0.00013541, 'Monte_Carlo_Max_Return': 0.00666288, 'Monte_Carlo_Min_CVaR': 0.00812915, 'Monte_Carlo_Min_Volatility': 0.00418423, 'Portefeuille recommande': 0.00202696, 'Risk_Parity': 0.00618228}</t>
+          <t>{'Current_Portfolio': 0.0001354, 'Max_Return': 0.0, 'MeanVariance_TurnoverPenalty': 0.00617435, 'Mean_CVaR_95': 0.00202696, 'Mean_Variance_lambda_10': 1e-08, 'Mean_Variance_lambda_2': 0.0, 'Mean_Variance_lambda_20': 0.00617436, 'Mean_Variance_lambda_5': 0.0, 'Minimum_Variance': 0.00013541, 'Monte_Carlo_Max_Return': 0.01092499, 'Monte_Carlo_Min_CVaR': 0.00738725, 'Monte_Carlo_Min_Volatility': 0.00514017, 'Portefeuille recommande': 0.00202696, 'Risk_Parity': 0.00618228}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1801,31 +1801,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>510</v>
+        <v>88395</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1090600154706529</v>
+        <v>0.1090866215801427</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02198448540334217</v>
+        <v>0.01952380432443762</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004833175984497649</v>
+        <v>0.000381178935298929</v>
       </c>
       <c r="E2" t="n">
-        <v>1.485242492346589</v>
+        <v>1.673797660530908</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008609025357394577</v>
+        <v>0.0006293320889072926</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001556905428899847</v>
+        <v>0.001286324322656931</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.006531437835928466</v>
+        <v>-0.003811547039435204</v>
       </c>
       <c r="I2" t="n">
-        <v>0.299909746027158</v>
+        <v>0.2788120650808324</v>
       </c>
       <c r="J2" t="n">
         <v>0.3</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"BTA_7_4_02_2030": 0.08347557519515607, "BTA_7_5_12_2028": 0.08056537356642726, "EMPRUNT_NATIONAL_2021_2EME_TRANCHE": 0.07976255980101703, "EMPRUNT_NATIONAL_2022_3EME_TRANCHE_10_ANS": 0.04721198027543818, "EMPRUNT_NATIONAL_2023_4EME_TRANCHE_CATEGORIE_C": 0.04709808002075978, "TN0007310568": 0.008943775872834776, "TN0003100872": 0.033243273734527984, "TNHFN9X6ARP3": 0.03247485995499575, "TN8DSPQCBC06": 0.01645751810269096, "TNL7VQZVHR54": 0.2927463532044944, "TNYGOCQ2WZX6": 0.01879054555417538, "TNDE9EH7SA12": 0.014693726874631989, "EO_ATL_2025_2": 0.04367356141707316, "AMEN_BANK": 0.028203715127525536, "ATTIJARI_BANK": 0.044619945484303834, "BIAT": 0.01796885546898055, "BT": 0.011704594060702726, "CITY_CARS": 0.006662880024040906, "DELICE_HOLDING": 0.017046087409186898, "ENNAKL": 0.02716848693346201, "PGH": 0.04748825191757445}</t>
+          <t>{"BTA_7_4_02_2030": 0.0982193725255559, "BTA_7_5_12_2028": 0.07433824890612857, "EMPRUNT_NATIONAL_2021_2EME_TRANCHE": 0.07836346880716558, "EMPRUNT_NATIONAL_2022_3EME_TRANCHE_10_ANS": 0.03649750378295421, "EMPRUNT_NATIONAL_2023_4EME_TRANCHE_CATEGORIE_C": 0.0582872558577967, "TN0007310568": 0.017323847412894135, "TN0003100872": 0.017898098999508793, "TNHFN9X6ARP3": 0.03365357473843258, "TN8DSPQCBC06": 0.023777482919999197, "TNL7VQZVHR54": 0.2976823561765675, "TNYGOCQ2WZX6": 0.01272594186322387, "TNDE9EH7SA12": 0.01522018869741971, "EO_ATL_2025_2": 0.04338582142462224, "AMEN_BANK": 0.038429738616913706, "ATTIJARI_BANK": 0.02161282432810847, "BIAT": 0.017555086240322936, "BT": 0.019882678945388463, "CITY_CARS": 0.010924985608945418, "DELICE_HOLDING": 0.014940188841171343, "ENNAKL": 0.026018965256840935, "PGH": 0.04326237005003989}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1861,31 +1861,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21862</v>
+        <v>83744</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1070223573302517</v>
+        <v>0.1070964883751706</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01357600313482882</v>
+        <v>0.01295573070623824</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000184307861116882</v>
+        <v>0.0001678509581325644</v>
       </c>
       <c r="E3" t="n">
-        <v>2.255055000280236</v>
+        <v>2.36874055919965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004814059211946261</v>
+        <v>0.0004570227684024786</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009650259577490031</v>
+        <v>0.00090391619239096</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.002404769066065904</v>
+        <v>-0.002310303205266151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2662657133309652</v>
+        <v>0.2871893078548028</v>
       </c>
       <c r="J3" t="n">
         <v>0.3</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>{"BTA_7_4_02_2030": 0.11472472659200843, "BTA_7_5_12_2028": 0.08779435678555031, "EMPRUNT_NATIONAL_2021_2EME_TRANCHE": 0.11041108713490513, "EMPRUNT_NATIONAL_2022_3EME_TRANCHE_10_ANS": 0.0472476282420543, "EMPRUNT_NATIONAL_2023_4EME_TRANCHE_CATEGORIE_C": 0.0563850366736909, "TN0007310568": 0.010337935220603884, "TN0003100872": 0.0264902157967051, "TNHFN9X6ARP3": 0.03415020222879281, "TN8DSPQCBC06": 0.013271639758507488, "TNL7VQZVHR54": 0.2992085467855138, "TNYGOCQ2WZX6": 0.01662682449043304, "TNDE9EH7SA12": 0.011030528267575373, "EO_ATL_2025_2": 0.04218549081527617, "AMEN_BANK": 0.022936956998258286, "ATTIJARI_BANK": 0.02195730609308067, "BIAT": 0.008414142101108553, "BT": 0.009978870116546159, "CITY_CARS": 0.004184231153245957, "DELICE_HOLDING": 0.006177777397097514, "ENNAKL": 0.026043956897164558, "PGH": 0.030442540451881675}</t>
+          <t>{"BTA_7_4_02_2030": 0.1318707027987137, "BTA_7_5_12_2028": 0.08540795973255763, "EMPRUNT_NATIONAL_2021_2EME_TRANCHE": 0.07910251349386234, "EMPRUNT_NATIONAL_2022_3EME_TRANCHE_10_ANS": 0.04638218701717408, "EMPRUNT_NATIONAL_2023_4EME_TRANCHE_CATEGORIE_C": 0.053547632585711234, "TN0007310568": 0.01717855272240683, "TN0003100872": 0.033107469501467646, "TNHFN9X6ARP3": 0.05064578642064331, "TN8DSPQCBC06": 0.020188358590484786, "TNL7VQZVHR54": 0.2981486003312359, "TNYGOCQ2WZX6": 0.010554305642703132, "TNDE9EH7SA12": 0.013785256844816473, "EO_ATL_2025_2": 0.0368392119159533, "AMEN_BANK": 0.021111345932648403, "ATTIJARI_BANK": 0.01960210495662213, "BIAT": 0.008971394559192603, "BT": 0.006292510484956584, "CITY_CARS": 0.005140169237026637, "DELICE_HOLDING": 0.006550903788785863, "ENNAKL": 0.024640445047494727, "PGH": 0.03093258839554259}</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1921,31 +1921,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>12951</v>
+        <v>73726</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1074538657410433</v>
+        <v>0.1069539910657012</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01424344518591956</v>
+        <v>0.01354792180805781</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000202875730764295</v>
+        <v>0.0001835461853172485</v>
       </c>
       <c r="E4" t="n">
-        <v>2.179679267098828</v>
+        <v>2.254682889467051</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004630658604079524</v>
+        <v>0.0004243085024816404</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008514810283989937</v>
+        <v>0.0008288475983412187</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.002257815231675231</v>
+        <v>-0.002283374292154194</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2891861241422086</v>
+        <v>0.2895261288213622</v>
       </c>
       <c r="J4" t="n">
         <v>0.3</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>{"BTA_7_4_02_2030": 0.12202612294134009, "BTA_7_5_12_2028": 0.07618528069925216, "EMPRUNT_NATIONAL_2021_2EME_TRANCHE": 0.0877928842658951, "EMPRUNT_NATIONAL_2022_3EME_TRANCHE_10_ANS": 0.05767520420762611, "EMPRUNT_NATIONAL_2023_4EME_TRANCHE_CATEGORIE_C": 0.07217670525303752, "TN0007310568": 0.019929041606826542, "TN0003100872": 0.016905178916750214, "TNHFN9X6ARP3": 0.03629649040740371, "TN8DSPQCBC06": 0.011429132096316673, "TNL7VQZVHR54": 0.2970066918471766, "TNYGOCQ2WZX6": 0.011031377536949839, "TNDE9EH7SA12": 0.01801655579733887, "EO_ATL_2025_2": 0.0397960252645283, "AMEN_BANK": 0.0128032640344391, "ATTIJARI_BANK": 0.0173631430860527, "BIAT": 0.011329543784483205, "BT": 0.012846821519309916, "CITY_CARS": 0.00812914815834678, "DELICE_HOLDING": 0.013422943213248287, "ENNAKL": 0.02335759733923666, "PGH": 0.03448084802444175}</t>
+          <t>{"BTA_7_4_02_2030": 0.117438959337742, "BTA_7_5_12_2028": 0.0934269183591134, "EMPRUNT_NATIONAL_2021_2EME_TRANCHE": 0.09907254076682279, "EMPRUNT_NATIONAL_2022_3EME_TRANCHE_10_ANS": 0.0634176184852903, "EMPRUNT_NATIONAL_2023_4EME_TRANCHE_CATEGORIE_C": 0.0532030479785076, "TN0007310568": 0.011034227095935212, "TN0003100872": 0.02302610188467887, "TNHFN9X6ARP3": 0.026062775602044563, "TN8DSPQCBC06": 0.011887063648512929, "TNL7VQZVHR54": 0.29326861790687486, "TNYGOCQ2WZX6": 0.019294370746313332, "TNDE9EH7SA12": 0.02164091367113576, "EO_ATL_2025_2": 0.03978304482674875, "AMEN_BANK": 0.0167011133744585, "ATTIJARI_BANK": 0.01609497242568206, "BIAT": 0.008753248683672566, "BT": 0.009321042615339474, "CITY_CARS": 0.011031567144415031, "DELICE_HOLDING": 0.007387247307818355, "ENNAKL": 0.02357239599875863, "PGH": 0.034582212140135106}</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15000 simulations</t>
+          <t>50000 simulations</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10 fichiers</t>
+          <t>13 fichiers</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
